--- a/template_nhap_gia BacLieu.xlsx
+++ b/template_nhap_gia BacLieu.xlsx
@@ -32,7 +32,7 @@
     <t>ten_xe</t>
   </si>
   <si>
-    <t>PHƯỜNG BẠC LIÊU- VĨNH TRẠCH- HIỆP THÀNH</t>
+    <t>Phường Bạc Liêu, Phường Hiệp Thành, Phường Vĩnh Trạch</t>
   </si>
   <si>
     <t>HÒA BÌNH- VĨNH LỢI</t>
@@ -1276,7 +1276,7 @@
     <col min="8" max="8" width="21.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="44" spans="1:8">
+    <row r="1" spans="1:8">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
